--- a/MLBB_Meta_Tiers.xlsx
+++ b/MLBB_Meta_Tiers.xlsx
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="F2" t="n">
-        <v>92.97</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>92.38</v>
+        <v>92.34</v>
       </c>
       <c r="H2" t="n">
         <v>0.59</v>
       </c>
       <c r="I2" t="n">
-        <v>54.4</v>
+        <v>54.46</v>
       </c>
       <c r="J2" t="n">
         <v>5.9</v>
@@ -554,22 +554,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>83.81</v>
+        <v>84.09</v>
       </c>
       <c r="G3" t="n">
-        <v>82.65000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="H3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="I3" t="n">
-        <v>53.55</v>
+        <v>53.6</v>
       </c>
       <c r="J3" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="4">
@@ -590,22 +590,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>85.90000000000001</v>
+        <v>85.75</v>
       </c>
       <c r="G4" t="n">
-        <v>84.93000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I4" t="n">
-        <v>50.67</v>
+        <v>50.7</v>
       </c>
       <c r="J4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
@@ -629,16 +629,16 @@
         <v>35.4</v>
       </c>
       <c r="F5" t="n">
-        <v>51.55</v>
+        <v>51.54</v>
       </c>
       <c r="G5" t="n">
-        <v>50.17</v>
+        <v>50.16</v>
       </c>
       <c r="H5" t="n">
         <v>1.38</v>
       </c>
       <c r="I5" t="n">
-        <v>51.2</v>
+        <v>51.21</v>
       </c>
       <c r="J5" t="n">
         <v>13.8</v>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="F6" t="n">
-        <v>18.98</v>
+        <v>18.71</v>
       </c>
       <c r="G6" t="n">
-        <v>18.65</v>
+        <v>18.38</v>
       </c>
       <c r="H6" t="n">
         <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>55.58</v>
+        <v>55.52</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="F7" t="n">
-        <v>36.76</v>
+        <v>36.27</v>
       </c>
       <c r="G7" t="n">
-        <v>35.64</v>
+        <v>35.15</v>
       </c>
       <c r="H7" t="n">
         <v>1.12</v>
       </c>
       <c r="I7" t="n">
-        <v>52.88</v>
+        <v>52.86</v>
       </c>
       <c r="J7" t="n">
         <v>11.2</v>
@@ -737,16 +737,16 @@
         <v>31.2</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81</v>
+        <v>21.76</v>
       </c>
       <c r="G8" t="n">
-        <v>20.59</v>
+        <v>20.54</v>
       </c>
       <c r="H8" t="n">
         <v>1.22</v>
       </c>
       <c r="I8" t="n">
-        <v>54.49</v>
+        <v>54.5</v>
       </c>
       <c r="J8" t="n">
         <v>12.2</v>
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="F9" t="n">
-        <v>48.34</v>
+        <v>48.12</v>
       </c>
       <c r="G9" t="n">
-        <v>47.56</v>
+        <v>47.34</v>
       </c>
       <c r="H9" t="n">
         <v>0.78</v>
@@ -806,22 +806,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="F10" t="n">
-        <v>41.59</v>
+        <v>41.6</v>
       </c>
       <c r="G10" t="n">
-        <v>40.49</v>
+        <v>40.51</v>
       </c>
       <c r="H10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
-        <v>51.17</v>
+        <v>51.15</v>
       </c>
       <c r="J10" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="11">
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="F11" t="n">
-        <v>39.62</v>
+        <v>39.5</v>
       </c>
       <c r="G11" t="n">
-        <v>37.5</v>
+        <v>37.38</v>
       </c>
       <c r="H11" t="n">
         <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>51.06</v>
+        <v>51.03</v>
       </c>
       <c r="J11" t="n">
         <v>21.2</v>
@@ -878,22 +878,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="F12" t="n">
-        <v>26.89</v>
+        <v>26.81</v>
       </c>
       <c r="G12" t="n">
-        <v>25.85</v>
+        <v>25.78</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I12" t="n">
-        <v>52.63</v>
+        <v>52.67</v>
       </c>
       <c r="J12" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="13">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="G13" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="n">
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>56.48</v>
+        <v>56.46</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
@@ -950,22 +950,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="F14" t="n">
-        <v>24.33</v>
+        <v>24.49</v>
       </c>
       <c r="G14" t="n">
-        <v>23.43</v>
+        <v>23.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="I14" t="n">
-        <v>52.55</v>
+        <v>52.57</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="15">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="F15" t="n">
-        <v>12.98</v>
+        <v>13.22</v>
       </c>
       <c r="G15" t="n">
-        <v>12.39</v>
+        <v>12.62</v>
       </c>
       <c r="H15" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="n">
-        <v>54.14</v>
+        <v>54.15</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="F16" t="n">
-        <v>25.03</v>
+        <v>25.68</v>
       </c>
       <c r="G16" t="n">
-        <v>23.92</v>
+        <v>24.57</v>
       </c>
       <c r="H16" t="n">
         <v>1.11</v>
@@ -1094,19 +1094,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
-        <v>24.06</v>
+        <v>23.68</v>
       </c>
       <c r="G18" t="n">
-        <v>23.24</v>
+        <v>22.86</v>
       </c>
       <c r="H18" t="n">
         <v>0.82</v>
       </c>
       <c r="I18" t="n">
-        <v>52.21</v>
+        <v>52.22</v>
       </c>
       <c r="J18" t="n">
         <v>8.199999999999999</v>
@@ -1133,19 +1133,19 @@
         <v>22.5</v>
       </c>
       <c r="F19" t="n">
-        <v>23.01</v>
+        <v>23.44</v>
       </c>
       <c r="G19" t="n">
-        <v>21.21</v>
+        <v>21.66</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="I19" t="n">
-        <v>52.22</v>
+        <v>52.16</v>
       </c>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="20">
@@ -1157,31 +1157,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kaja</t>
+          <t>Zetian</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hidden OP (The Specialist)</t>
+          <t>A-Tier (Comfort Staple)</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>21.5</v>
       </c>
       <c r="F20" t="n">
-        <v>5.1</v>
+        <v>19.18</v>
       </c>
       <c r="G20" t="n">
-        <v>4.65</v>
+        <v>17.02</v>
       </c>
       <c r="H20" t="n">
-        <v>0.45</v>
+        <v>2.16</v>
       </c>
       <c r="I20" t="n">
-        <v>54.61</v>
+        <v>52.55</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,31 +1193,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zetian</t>
+          <t>Kaja</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A-Tier (Comfort Staple)</t>
+          <t>Hidden OP (The Specialist)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="F21" t="n">
-        <v>18.83</v>
+        <v>5.11</v>
       </c>
       <c r="G21" t="n">
-        <v>16.67</v>
+        <v>4.66</v>
       </c>
       <c r="H21" t="n">
-        <v>2.16</v>
+        <v>0.45</v>
       </c>
       <c r="I21" t="n">
-        <v>52.51</v>
+        <v>54.58</v>
       </c>
       <c r="J21" t="n">
-        <v>21.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="22">
@@ -1238,22 +1238,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="F22" t="n">
-        <v>12.94</v>
+        <v>12.9</v>
       </c>
       <c r="G22" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
       <c r="H22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I22" t="n">
-        <v>52.84</v>
+        <v>52.82</v>
       </c>
       <c r="J22" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="23">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="F23" t="n">
-        <v>11.77</v>
+        <v>11.72</v>
       </c>
       <c r="G23" t="n">
-        <v>10.49</v>
+        <v>10.44</v>
       </c>
       <c r="H23" t="n">
         <v>1.28</v>
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="F24" t="n">
-        <v>6.64</v>
+        <v>6.53</v>
       </c>
       <c r="G24" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="H24" t="n">
         <v>0.7</v>
       </c>
       <c r="I24" t="n">
-        <v>53.55</v>
+        <v>53.59</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
@@ -1337,31 +1337,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leomord</t>
+          <t>Hanabi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B-Tier (Reliable / Strong)</t>
+          <t>A-Tier (Comfort Staple)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="F25" t="n">
-        <v>13.26</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>12.25</v>
+        <v>4.32</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="I25" t="n">
-        <v>52.48</v>
+        <v>53.36</v>
       </c>
       <c r="J25" t="n">
-        <v>10.1</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="26">
@@ -1382,22 +1382,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.49</v>
+        <v>11.72</v>
       </c>
       <c r="G26" t="n">
-        <v>9.970000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="H26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I26" t="n">
-        <v>52.62</v>
+        <v>52.64</v>
       </c>
       <c r="J26" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="27">
@@ -1409,31 +1409,31 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hanabi</t>
+          <t>Leomord</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A-Tier (Comfort Staple)</t>
+          <t>B-Tier (Reliable / Strong)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="F27" t="n">
-        <v>6.56</v>
+        <v>12.82</v>
       </c>
       <c r="G27" t="n">
-        <v>4.02</v>
+        <v>11.83</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>53.32</v>
+        <v>52.47</v>
       </c>
       <c r="J27" t="n">
-        <v>25.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="28">
@@ -1454,22 +1454,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="F28" t="n">
-        <v>21.19</v>
+        <v>21.07</v>
       </c>
       <c r="G28" t="n">
-        <v>19.07</v>
+        <v>18.96</v>
       </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="I28" t="n">
-        <v>50.41</v>
+        <v>50.39</v>
       </c>
       <c r="J28" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="29">
@@ -1493,16 +1493,16 @@
         <v>13.1</v>
       </c>
       <c r="F29" t="n">
-        <v>15.65</v>
+        <v>15.63</v>
       </c>
       <c r="G29" t="n">
-        <v>15.1</v>
+        <v>15.08</v>
       </c>
       <c r="H29" t="n">
         <v>0.55</v>
       </c>
       <c r="I29" t="n">
-        <v>50.97</v>
+        <v>50.96</v>
       </c>
       <c r="J29" t="n">
         <v>5.5</v>
@@ -1529,16 +1529,16 @@
         <v>12.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H30" t="n">
         <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>52.97</v>
+        <v>52.96</v>
       </c>
       <c r="J30" t="n">
         <v>5</v>
@@ -1562,22 +1562,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="F31" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="G31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H31" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>52.76</v>
+        <v>52.8</v>
       </c>
       <c r="J31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="32">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F32" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G32" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H32" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I32" t="n">
-        <v>52.79</v>
+        <v>52.81</v>
       </c>
       <c r="J32" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="33">
@@ -1637,16 +1637,16 @@
         <v>11.7</v>
       </c>
       <c r="F33" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="H33" t="n">
         <v>0.82</v>
       </c>
       <c r="I33" t="n">
-        <v>52.74</v>
+        <v>52.73</v>
       </c>
       <c r="J33" t="n">
         <v>8.199999999999999</v>
@@ -1670,22 +1670,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G34" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="H34" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I34" t="n">
-        <v>52.46</v>
+        <v>52.41</v>
       </c>
       <c r="J34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="35">
@@ -1709,19 +1709,19 @@
         <v>10.1</v>
       </c>
       <c r="F35" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G35" t="n">
         <v>0.55</v>
       </c>
       <c r="H35" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="I35" t="n">
         <v>52.36</v>
       </c>
       <c r="J35" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="36">
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="F36" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="G36" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
         <v>0.76</v>
       </c>
       <c r="I36" t="n">
-        <v>52.09</v>
+        <v>52.05</v>
       </c>
       <c r="J36" t="n">
         <v>7.6</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F37" t="n">
         <v>3.23</v>
@@ -1790,7 +1790,7 @@
         <v>1.51</v>
       </c>
       <c r="I37" t="n">
-        <v>51.92</v>
+        <v>51.87</v>
       </c>
       <c r="J37" t="n">
         <v>15.1</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F38" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="G38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H38" t="n">
         <v>0.78</v>
       </c>
       <c r="I38" t="n">
-        <v>51.91</v>
+        <v>51.92</v>
       </c>
       <c r="J38" t="n">
         <v>7.8</v>
@@ -1853,19 +1853,19 @@
         <v>8.9</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G39" t="n">
         <v>0.17</v>
       </c>
       <c r="H39" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="I39" t="n">
         <v>52.14</v>
       </c>
       <c r="J39" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="40">
@@ -1889,16 +1889,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>9.130000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="H40" t="n">
         <v>0.62</v>
       </c>
       <c r="I40" t="n">
-        <v>50.78</v>
+        <v>50.77</v>
       </c>
       <c r="J40" t="n">
         <v>6.2</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="F41" t="n">
         <v>0.54</v>
@@ -1934,7 +1934,7 @@
         <v>0.44</v>
       </c>
       <c r="I41" t="n">
-        <v>52.02</v>
+        <v>52.05</v>
       </c>
       <c r="J41" t="n">
         <v>4.4</v>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F42" t="n">
-        <v>17.56</v>
+        <v>17.32</v>
       </c>
       <c r="G42" t="n">
-        <v>16.45</v>
+        <v>16.22</v>
       </c>
       <c r="H42" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I42" t="n">
         <v>49.44</v>
       </c>
       <c r="J42" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Odette</t>
+          <t>Uranus</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1994,22 +1994,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="F43" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="G43" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="H43" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="I43" t="n">
-        <v>51.79</v>
+        <v>51.73</v>
       </c>
       <c r="J43" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="44">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Uranus</t>
+          <t>Odette</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2033,19 +2033,19 @@
         <v>7.6</v>
       </c>
       <c r="F44" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="G44" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="H44" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="I44" t="n">
-        <v>51.73</v>
+        <v>51.76</v>
       </c>
       <c r="J44" t="n">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Khaleed</t>
+          <t>Argus</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2066,22 +2066,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="G45" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="H45" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="I45" t="n">
-        <v>51.7</v>
+        <v>51.79</v>
       </c>
       <c r="J45" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="46">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argus</t>
+          <t>Khaleed</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="F46" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="H46" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="I46" t="n">
         <v>51.73</v>
       </c>
       <c r="J46" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="47">
@@ -2141,16 +2141,16 @@
         <v>6.9</v>
       </c>
       <c r="F47" t="n">
-        <v>14.95</v>
+        <v>14.81</v>
       </c>
       <c r="G47" t="n">
-        <v>13.2</v>
+        <v>13.06</v>
       </c>
       <c r="H47" t="n">
         <v>1.75</v>
       </c>
       <c r="I47" t="n">
-        <v>49.65</v>
+        <v>49.67</v>
       </c>
       <c r="J47" t="n">
         <v>17.5</v>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bane</t>
+          <t>Yu Zhong</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2177,19 +2177,19 @@
         <v>5.9</v>
       </c>
       <c r="F48" t="n">
-        <v>0.43</v>
+        <v>7.87</v>
       </c>
       <c r="G48" t="n">
-        <v>0.09</v>
+        <v>6.51</v>
       </c>
       <c r="H48" t="n">
-        <v>0.34</v>
+        <v>1.36</v>
       </c>
       <c r="I48" t="n">
-        <v>51.44</v>
+        <v>50.4</v>
       </c>
       <c r="J48" t="n">
-        <v>3.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="49">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Faramis</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="F49" t="n">
-        <v>0.85</v>
+        <v>2.14</v>
       </c>
       <c r="G49" t="n">
-        <v>0.66</v>
+        <v>1.86</v>
       </c>
       <c r="H49" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="I49" t="n">
-        <v>51.36</v>
+        <v>51.11</v>
       </c>
       <c r="J49" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="50">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Yu Zhong</t>
+          <t>Bane</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2246,22 +2246,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="F50" t="n">
-        <v>7.95</v>
+        <v>0.43</v>
       </c>
       <c r="G50" t="n">
-        <v>6.58</v>
+        <v>0.09</v>
       </c>
       <c r="H50" t="n">
-        <v>1.37</v>
+        <v>0.34</v>
       </c>
       <c r="I50" t="n">
-        <v>50.4</v>
+        <v>51.36</v>
       </c>
       <c r="J50" t="n">
-        <v>13.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="51">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Yve</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2282,22 +2282,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="F51" t="n">
-        <v>2.13</v>
+        <v>0.31</v>
       </c>
       <c r="G51" t="n">
-        <v>1.85</v>
+        <v>0.11</v>
       </c>
       <c r="H51" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>51.15</v>
+        <v>51.34</v>
       </c>
       <c r="J51" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Popol and Kupa</t>
+          <t>Faramis</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2318,22 +2318,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="G52" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="H52" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="I52" t="n">
-        <v>51.36</v>
+        <v>51.26</v>
       </c>
       <c r="J52" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="53">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yve</t>
+          <t>Popol and Kupa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2357,19 +2357,19 @@
         <v>5.5</v>
       </c>
       <c r="F53" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G53" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="I53" t="n">
         <v>51.34</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="54">
@@ -2393,10 +2393,10 @@
         <v>5.3</v>
       </c>
       <c r="F54" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="G54" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="H54" t="n">
         <v>0.6899999999999999</v>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="F55" t="n">
         <v>1.53</v>
@@ -2438,7 +2438,7 @@
         <v>0.75</v>
       </c>
       <c r="I55" t="n">
-        <v>51.12</v>
+        <v>51.14</v>
       </c>
       <c r="J55" t="n">
         <v>7.5</v>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Clint</t>
+          <t>Thamuz</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2465,19 +2465,19 @@
         <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>1.75</v>
+        <v>3.19</v>
       </c>
       <c r="G56" t="n">
-        <v>0.75</v>
+        <v>2.29</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I56" t="n">
-        <v>51.06</v>
+        <v>50.82</v>
       </c>
       <c r="J56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thamuz</t>
+          <t>Aulus</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2501,19 +2501,19 @@
         <v>4.9</v>
       </c>
       <c r="F57" t="n">
-        <v>3.13</v>
+        <v>0.17</v>
       </c>
       <c r="G57" t="n">
-        <v>2.24</v>
+        <v>0.05</v>
       </c>
       <c r="H57" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="I57" t="n">
-        <v>50.82</v>
+        <v>51.2</v>
       </c>
       <c r="J57" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="58">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Suyou</t>
+          <t>Clint</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2537,19 +2537,19 @@
         <v>4.7</v>
       </c>
       <c r="F58" t="n">
-        <v>3.28</v>
+        <v>1.73</v>
       </c>
       <c r="G58" t="n">
-        <v>2.04</v>
+        <v>0.74</v>
       </c>
       <c r="H58" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="I58" t="n">
-        <v>50.77</v>
+        <v>50.99</v>
       </c>
       <c r="J58" t="n">
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="59">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aulus</t>
+          <t>Suyou</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2570,22 +2570,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="F59" t="n">
-        <v>0.16</v>
+        <v>3.29</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05</v>
+        <v>2.05</v>
       </c>
       <c r="H59" t="n">
-        <v>0.11</v>
+        <v>1.24</v>
       </c>
       <c r="I59" t="n">
-        <v>51.1</v>
+        <v>50.77</v>
       </c>
       <c r="J59" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="60">
@@ -2618,7 +2618,7 @@
         <v>0.7</v>
       </c>
       <c r="I60" t="n">
-        <v>50.92</v>
+        <v>50.94</v>
       </c>
       <c r="J60" t="n">
         <v>7</v>
@@ -2642,19 +2642,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="F61" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="G61" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="H61" t="n">
         <v>1.19</v>
       </c>
       <c r="I61" t="n">
-        <v>50.6</v>
+        <v>50.58</v>
       </c>
       <c r="J61" t="n">
         <v>11.9</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brody</t>
+          <t>Cyclops</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2681,19 +2681,19 @@
         <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="G62" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="H62" t="n">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="I62" t="n">
-        <v>50.91</v>
+        <v>50.83</v>
       </c>
       <c r="J62" t="n">
-        <v>6.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="63">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cyclops</t>
+          <t>Alucard</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2717,19 +2717,19 @@
         <v>3.8</v>
       </c>
       <c r="F63" t="n">
-        <v>1.59</v>
+        <v>1.13</v>
       </c>
       <c r="G63" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H63" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="I63" t="n">
-        <v>50.79</v>
+        <v>50.82</v>
       </c>
       <c r="J63" t="n">
-        <v>10.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="64">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Alucard</t>
+          <t>Brody</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2753,19 +2753,19 @@
         <v>3.7</v>
       </c>
       <c r="F64" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H64" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="I64" t="n">
-        <v>50.79</v>
+        <v>50.83</v>
       </c>
       <c r="J64" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="65">
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="F65" t="n">
         <v>2.39</v>
@@ -2798,7 +2798,7 @@
         <v>1.64</v>
       </c>
       <c r="I65" t="n">
-        <v>50.6</v>
+        <v>50.58</v>
       </c>
       <c r="J65" t="n">
         <v>16.4</v>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="F66" t="n">
         <v>0.44</v>
@@ -2834,7 +2834,7 @@
         <v>0.18</v>
       </c>
       <c r="I66" t="n">
-        <v>50.71</v>
+        <v>50.76</v>
       </c>
       <c r="J66" t="n">
         <v>1.8</v>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Edith</t>
+          <t>Terizla</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2861,19 +2861,19 @@
         <v>2.9</v>
       </c>
       <c r="F67" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="G67" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H67" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="I67" t="n">
-        <v>50.69</v>
+        <v>50.67</v>
       </c>
       <c r="J67" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="68">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Terizla</t>
+          <t>Edith</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2897,19 +2897,19 @@
         <v>2.8</v>
       </c>
       <c r="F68" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="G68" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H68" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="I68" t="n">
-        <v>50.65</v>
+        <v>50.66</v>
       </c>
       <c r="J68" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="69">
@@ -2933,19 +2933,19 @@
         <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G69" t="n">
         <v>1.12</v>
       </c>
       <c r="H69" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I69" t="n">
         <v>50.29</v>
       </c>
       <c r="J69" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="70">
@@ -2966,22 +2966,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F70" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G70" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I70" t="n">
-        <v>50.14</v>
+        <v>50.18</v>
       </c>
       <c r="J70" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="71">
@@ -3002,13 +3002,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F71" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G71" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="H71" t="n">
         <v>0.85</v>
@@ -3038,19 +3038,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F72" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="G72" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="H72" t="n">
         <v>0.5</v>
       </c>
       <c r="I72" t="n">
-        <v>50.02</v>
+        <v>50.01</v>
       </c>
       <c r="J72" t="n">
         <v>5</v>
@@ -3074,22 +3074,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F73" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I73" t="n">
-        <v>50</v>
+        <v>50.01</v>
       </c>
       <c r="J73" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>X.Borg</t>
+          <t>Belerick</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3113,19 +3113,19 @@
         <v>0.2</v>
       </c>
       <c r="F74" t="n">
-        <v>5.83</v>
+        <v>4.48</v>
       </c>
       <c r="G74" t="n">
-        <v>4.97</v>
+        <v>3.46</v>
       </c>
       <c r="H74" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="I74" t="n">
-        <v>49.26</v>
+        <v>49.47</v>
       </c>
       <c r="J74" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="75">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belerick</t>
+          <t>X.Borg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3146,22 +3146,22 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F75" t="n">
-        <v>4.39</v>
+        <v>5.8</v>
       </c>
       <c r="G75" t="n">
-        <v>3.38</v>
+        <v>4.94</v>
       </c>
       <c r="H75" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="I75" t="n">
-        <v>49.43</v>
+        <v>49.27</v>
       </c>
       <c r="J75" t="n">
-        <v>10.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="76">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Vale</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3182,22 +3182,22 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="F76" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="G76" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="H76" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="I76" t="n">
-        <v>49.87</v>
+        <v>49.9</v>
       </c>
       <c r="J76" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="77">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3218,22 +3218,22 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="F77" t="n">
-        <v>1.71</v>
+        <v>1.05</v>
       </c>
       <c r="G77" t="n">
-        <v>1.23</v>
+        <v>0.17</v>
       </c>
       <c r="H77" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="I77" t="n">
-        <v>49.7</v>
+        <v>49.84</v>
       </c>
       <c r="J77" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vale</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3254,22 +3254,22 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4</v>
+        <v>1.71</v>
       </c>
       <c r="G78" t="n">
-        <v>0.05</v>
+        <v>1.23</v>
       </c>
       <c r="H78" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="I78" t="n">
-        <v>49.87</v>
+        <v>49.63</v>
       </c>
       <c r="J78" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="79">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F79" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="G79" t="n">
-        <v>7.37</v>
+        <v>7.28</v>
       </c>
       <c r="H79" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I79" t="n">
-        <v>48.74</v>
+        <v>48.73</v>
       </c>
       <c r="J79" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="80">
@@ -3338,7 +3338,7 @@
         <v>0.68</v>
       </c>
       <c r="I80" t="n">
-        <v>49.8</v>
+        <v>49.79</v>
       </c>
       <c r="J80" t="n">
         <v>6.8</v>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3362,22 +3362,22 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="F81" t="n">
-        <v>0.59</v>
+        <v>1.63</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2</v>
+        <v>1.09</v>
       </c>
       <c r="H81" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="I81" t="n">
-        <v>49.74</v>
+        <v>49.64</v>
       </c>
       <c r="J81" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="82">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3398,22 +3398,22 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="F82" t="n">
-        <v>1.65</v>
+        <v>0.6</v>
       </c>
       <c r="G82" t="n">
-        <v>1.11</v>
+        <v>0.21</v>
       </c>
       <c r="H82" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="I82" t="n">
-        <v>49.61</v>
+        <v>49.72</v>
       </c>
       <c r="J82" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="83">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aldous</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3434,22 +3434,22 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="F83" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="G83" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="H83" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="I83" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="J83" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Pharsa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3470,22 +3470,22 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="F84" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="G84" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="I84" t="n">
-        <v>49.37</v>
+        <v>49.36</v>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Lylia</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3509,19 +3509,19 @@
         <v>-2.2</v>
       </c>
       <c r="F85" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="G85" t="n">
-        <v>1.41</v>
+        <v>0.45</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>49.2</v>
+        <v>49.33</v>
       </c>
       <c r="J85" t="n">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="86">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pharsa</t>
+          <t>Aldous</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3542,22 +3542,22 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="F86" t="n">
-        <v>1.28</v>
+        <v>0.54</v>
       </c>
       <c r="G86" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H86" t="n">
-        <v>0.98</v>
+        <v>0.32</v>
       </c>
       <c r="I86" t="n">
-        <v>49.37</v>
+        <v>49.38</v>
       </c>
       <c r="J86" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="87">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lylia</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3578,22 +3578,22 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="F87" t="n">
-        <v>1.31</v>
+        <v>2.13</v>
       </c>
       <c r="G87" t="n">
-        <v>0.41</v>
+        <v>1.43</v>
       </c>
       <c r="H87" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I87" t="n">
-        <v>49.29</v>
+        <v>49.14</v>
       </c>
       <c r="J87" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -3614,22 +3614,22 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="F88" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G88" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="H88" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I88" t="n">
-        <v>49.04</v>
+        <v>49.02</v>
       </c>
       <c r="J88" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="89">
@@ -3650,22 +3650,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="F89" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="G89" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H89" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I89" t="n">
-        <v>48.71</v>
+        <v>48.75</v>
       </c>
       <c r="J89" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="90">
@@ -3686,19 +3686,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="F90" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G90" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="H90" t="n">
         <v>0.52</v>
       </c>
       <c r="I90" t="n">
-        <v>48.73</v>
+        <v>48.72</v>
       </c>
       <c r="J90" t="n">
         <v>5.2</v>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Chang'e</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3722,22 +3722,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>-4.4</v>
+        <v>-4.6</v>
       </c>
       <c r="F91" t="n">
-        <v>2.75</v>
+        <v>0.96</v>
       </c>
       <c r="G91" t="n">
-        <v>1.3</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>1.45</v>
+        <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>48.67</v>
+        <v>48.79</v>
       </c>
       <c r="J91" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="92">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chang'e</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3761,19 +3761,19 @@
         <v>-4.7</v>
       </c>
       <c r="F92" t="n">
-        <v>0.96</v>
+        <v>2.67</v>
       </c>
       <c r="G92" t="n">
-        <v>0.24</v>
+        <v>1.25</v>
       </c>
       <c r="H92" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>48.77</v>
+        <v>48.61</v>
       </c>
       <c r="J92" t="n">
-        <v>7.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="93">
@@ -3830,22 +3830,22 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
       <c r="F94" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
       <c r="G94" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="H94" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I94" t="n">
-        <v>47.94</v>
+        <v>47.88</v>
       </c>
       <c r="J94" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="95">
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="F95" t="n">
         <v>0.82</v>
@@ -3878,7 +3878,7 @@
         <v>0.53</v>
       </c>
       <c r="I95" t="n">
-        <v>48.42</v>
+        <v>48.45</v>
       </c>
       <c r="J95" t="n">
         <v>5.3</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Beatrix</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3905,19 +3905,19 @@
         <v>-6.2</v>
       </c>
       <c r="F96" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="G96" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="H96" t="n">
-        <v>0.18</v>
+        <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>48.43</v>
+        <v>48.41</v>
       </c>
       <c r="J96" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="97">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Beatrix</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3938,22 +3938,22 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8</v>
+        <v>0.21</v>
       </c>
       <c r="G97" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="H97" t="n">
-        <v>0.65</v>
+        <v>0.17</v>
       </c>
       <c r="I97" t="n">
-        <v>48.41</v>
+        <v>48.36</v>
       </c>
       <c r="J97" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="98">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>-6.9</v>
+        <v>-7.3</v>
       </c>
       <c r="F98" t="n">
         <v>0.55</v>
@@ -3986,7 +3986,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>48.19</v>
+        <v>48.1</v>
       </c>
       <c r="J98" t="n">
         <v>0.7</v>
@@ -4010,22 +4010,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="G99" t="n">
         <v>0.15</v>
       </c>
       <c r="H99" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="I99" t="n">
-        <v>48.15</v>
+        <v>48.13</v>
       </c>
       <c r="J99" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="100">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Harley</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4046,22 +4046,22 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>-7.7</v>
+        <v>-7.5</v>
       </c>
       <c r="F100" t="n">
-        <v>0.41</v>
+        <v>1.34</v>
       </c>
       <c r="G100" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H100" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="I100" t="n">
-        <v>48.07</v>
+        <v>48.02</v>
       </c>
       <c r="J100" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Harley</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4082,22 +4082,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="F101" t="n">
-        <v>1.32</v>
+        <v>0.41</v>
       </c>
       <c r="G101" t="n">
-        <v>0.62</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="I101" t="n">
-        <v>47.97</v>
+        <v>48.09</v>
       </c>
       <c r="J101" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="102">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cici</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4121,19 +4121,19 @@
         <v>-8.4</v>
       </c>
       <c r="F102" t="n">
-        <v>0.34</v>
+        <v>1.49</v>
       </c>
       <c r="G102" t="n">
-        <v>0.06</v>
+        <v>0.89</v>
       </c>
       <c r="H102" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="I102" t="n">
-        <v>47.9</v>
+        <v>47.76</v>
       </c>
       <c r="J102" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cici</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4157,19 +4157,19 @@
         <v>-8.5</v>
       </c>
       <c r="F103" t="n">
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="G103" t="n">
-        <v>0.89</v>
+        <v>0.06</v>
       </c>
       <c r="H103" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="I103" t="n">
-        <v>47.74</v>
+        <v>47.87</v>
       </c>
       <c r="J103" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="104">
@@ -4190,19 +4190,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="F104" t="n">
-        <v>8.380000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="G104" t="n">
-        <v>6.34</v>
+        <v>6.37</v>
       </c>
       <c r="H104" t="n">
         <v>2.04</v>
       </c>
       <c r="I104" t="n">
-        <v>46.95</v>
+        <v>46.93</v>
       </c>
       <c r="J104" t="n">
         <v>20.4</v>
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="F105" t="n">
         <v>1.4</v>
@@ -4238,7 +4238,7 @@
         <v>0.9</v>
       </c>
       <c r="I105" t="n">
-        <v>47.77</v>
+        <v>47.73</v>
       </c>
       <c r="J105" t="n">
         <v>9</v>
@@ -4262,19 +4262,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="G106" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H106" t="n">
         <v>0.16</v>
       </c>
       <c r="I106" t="n">
-        <v>47.85</v>
+        <v>47.78</v>
       </c>
       <c r="J106" t="n">
         <v>1.6</v>
@@ -4301,19 +4301,19 @@
         <v>-8.9</v>
       </c>
       <c r="F107" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G107" t="n">
         <v>0.24</v>
       </c>
       <c r="H107" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I107" t="n">
-        <v>47.74</v>
+        <v>47.73</v>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="108">
@@ -4325,31 +4325,31 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Martis</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Solo-Queue Trap (Avoid at all costs)</t>
+          <t>C-Tier (Situational / Average)</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>-9.4</v>
+        <v>-9.5</v>
       </c>
       <c r="F108" t="n">
-        <v>12.23</v>
+        <v>0.63</v>
       </c>
       <c r="G108" t="n">
-        <v>10.59</v>
+        <v>0.19</v>
       </c>
       <c r="H108" t="n">
-        <v>1.64</v>
+        <v>0.44</v>
       </c>
       <c r="I108" t="n">
-        <v>46.13</v>
+        <v>47.6</v>
       </c>
       <c r="J108" t="n">
-        <v>16.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="109">
@@ -4361,31 +4361,31 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Martis</t>
+          <t>Franco</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>C-Tier (Situational / Average)</t>
+          <t>Solo-Queue Trap (Avoid at all costs)</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="F109" t="n">
-        <v>0.63</v>
+        <v>12.16</v>
       </c>
       <c r="G109" t="n">
-        <v>0.19</v>
+        <v>10.53</v>
       </c>
       <c r="H109" t="n">
-        <v>0.44</v>
+        <v>1.63</v>
       </c>
       <c r="I109" t="n">
-        <v>47.51</v>
+        <v>46.09</v>
       </c>
       <c r="J109" t="n">
-        <v>4.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="110">
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>-10.6</v>
+        <v>-10.8</v>
       </c>
       <c r="F110" t="n">
         <v>0.76</v>
@@ -4418,7 +4418,7 @@
         <v>0.48</v>
       </c>
       <c r="I110" t="n">
-        <v>47.3</v>
+        <v>47.27</v>
       </c>
       <c r="J110" t="n">
         <v>4.8</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>-12</v>
+        <v>-11.8</v>
       </c>
       <c r="F111" t="n">
         <v>0.93</v>
@@ -4454,7 +4454,7 @@
         <v>0.78</v>
       </c>
       <c r="I111" t="n">
-        <v>46.98</v>
+        <v>47.04</v>
       </c>
       <c r="J111" t="n">
         <v>7.8</v>
@@ -4490,7 +4490,7 @@
         <v>0.17</v>
       </c>
       <c r="I112" t="n">
-        <v>46.98</v>
+        <v>46.96</v>
       </c>
       <c r="J112" t="n">
         <v>1.7</v>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>-12.4</v>
+        <v>-12.5</v>
       </c>
       <c r="F113" t="n">
         <v>0.57</v>
@@ -4526,7 +4526,7 @@
         <v>0.43</v>
       </c>
       <c r="I113" t="n">
-        <v>46.88</v>
+        <v>46.85</v>
       </c>
       <c r="J113" t="n">
         <v>4.3</v>
@@ -4550,22 +4550,22 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>-12.7</v>
+        <v>-12.6</v>
       </c>
       <c r="F114" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="G114" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H114" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I114" t="n">
-        <v>46.79</v>
+        <v>46.81</v>
       </c>
       <c r="J114" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="115">
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>-12.9</v>
+        <v>-12.8</v>
       </c>
       <c r="F115" t="n">
         <v>0.89</v>
@@ -4598,7 +4598,7 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>46.74</v>
+        <v>46.77</v>
       </c>
       <c r="J115" t="n">
         <v>6.4</v>
@@ -4622,19 +4622,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>-13.7</v>
+        <v>-13.8</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="G116" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H116" t="n">
         <v>0.55</v>
       </c>
       <c r="I116" t="n">
-        <v>46.53</v>
+        <v>46.5</v>
       </c>
       <c r="J116" t="n">
         <v>5.5</v>
@@ -4658,22 +4658,22 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>-14.5</v>
+        <v>-14.3</v>
       </c>
       <c r="F117" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G117" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>46.28</v>
+        <v>46.34</v>
       </c>
       <c r="J117" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="118">
@@ -4694,19 +4694,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>-15.3</v>
+        <v>-15.2</v>
       </c>
       <c r="F118" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G118" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="H118" t="n">
         <v>0.48</v>
       </c>
       <c r="I118" t="n">
-        <v>46.1</v>
+        <v>46.11</v>
       </c>
       <c r="J118" t="n">
         <v>4.8</v>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wanwan</t>
+          <t>Kalea</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4730,22 +4730,22 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>-15.4</v>
+        <v>-15.5</v>
       </c>
       <c r="F119" t="n">
-        <v>0.4</v>
+        <v>2.06</v>
       </c>
       <c r="G119" t="n">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="I119" t="n">
-        <v>46.13</v>
+        <v>45.87</v>
       </c>
       <c r="J119" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="120">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kalea</t>
+          <t>Wanwan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4766,22 +4766,22 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>-15.6</v>
+        <v>-15.7</v>
       </c>
       <c r="F120" t="n">
-        <v>2.09</v>
+        <v>0.4</v>
       </c>
       <c r="G120" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H120" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="I120" t="n">
-        <v>45.83</v>
+        <v>46.04</v>
       </c>
       <c r="J120" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>-16</v>
+        <v>-16.5</v>
       </c>
       <c r="F121" t="n">
         <v>0.34</v>
@@ -4814,7 +4814,7 @@
         <v>0.24</v>
       </c>
       <c r="I121" t="n">
-        <v>46</v>
+        <v>45.88</v>
       </c>
       <c r="J121" t="n">
         <v>2.4</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>-18.5</v>
+        <v>-19</v>
       </c>
       <c r="F122" t="n">
         <v>0.31</v>
@@ -4850,7 +4850,7 @@
         <v>0.25</v>
       </c>
       <c r="I122" t="n">
-        <v>45.37</v>
+        <v>45.25</v>
       </c>
       <c r="J122" t="n">
         <v>2.5</v>
@@ -4874,22 +4874,22 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>-20.6</v>
+        <v>-20.2</v>
       </c>
       <c r="F123" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="G123" t="n">
         <v>1.3</v>
       </c>
       <c r="H123" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>44.71</v>
+        <v>44.8</v>
       </c>
       <c r="J123" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4910,22 +4910,22 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>-21.1</v>
+        <v>-21.3</v>
       </c>
       <c r="F124" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G124" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H124" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I124" t="n">
-        <v>44.71</v>
+        <v>44.66</v>
       </c>
       <c r="J124" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="125">
@@ -4946,22 +4946,22 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>-22</v>
+        <v>-22.2</v>
       </c>
       <c r="F125" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="G125" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H125" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I125" t="n">
-        <v>44.3</v>
+        <v>44.26</v>
       </c>
       <c r="J125" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="126">
@@ -4985,19 +4985,19 @@
         <v>-22.7</v>
       </c>
       <c r="F126" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G126" t="n">
         <v>0.34</v>
       </c>
       <c r="H126" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="I126" t="n">
         <v>44.3</v>
       </c>
       <c r="J126" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="127">
@@ -5054,22 +5054,22 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>-25.4</v>
+        <v>-25.8</v>
       </c>
       <c r="F128" t="n">
-        <v>5.35</v>
+        <v>5.48</v>
       </c>
       <c r="G128" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="H128" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="I128" t="n">
-        <v>43.06</v>
+        <v>42.96</v>
       </c>
       <c r="J128" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="129">
@@ -5090,19 +5090,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>-28.2</v>
+        <v>-28.1</v>
       </c>
       <c r="F129" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="G129" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H129" t="n">
         <v>0.23</v>
       </c>
       <c r="I129" t="n">
-        <v>42.91</v>
+        <v>42.95</v>
       </c>
       <c r="J129" t="n">
         <v>2.3</v>
@@ -5129,19 +5129,19 @@
         <v>-28.9</v>
       </c>
       <c r="F130" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="G130" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="H130" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I130" t="n">
-        <v>42.43</v>
+        <v>42.44</v>
       </c>
       <c r="J130" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="131">
@@ -5162,22 +5162,22 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>-30</v>
+        <v>-30.2</v>
       </c>
       <c r="F131" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="G131" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="H131" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="I131" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="J131" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="132">
@@ -5198,22 +5198,22 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>-32.1</v>
+        <v>-32</v>
       </c>
       <c r="F132" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="G132" t="n">
         <v>0.16</v>
       </c>
       <c r="H132" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I132" t="n">
-        <v>41.97</v>
+        <v>42.01</v>
       </c>
       <c r="J132" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -5296,16 +5296,16 @@
         <v>31.2</v>
       </c>
       <c r="D2" t="n">
-        <v>21.81</v>
+        <v>21.76</v>
       </c>
       <c r="E2" t="n">
-        <v>20.59</v>
+        <v>20.54</v>
       </c>
       <c r="F2" t="n">
         <v>1.22</v>
       </c>
       <c r="G2" t="n">
-        <v>54.49</v>
+        <v>54.5</v>
       </c>
       <c r="H2" t="n">
         <v>12.2</v>
@@ -5321,22 +5321,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D3" t="n">
-        <v>26.89</v>
+        <v>26.81</v>
       </c>
       <c r="E3" t="n">
-        <v>25.85</v>
+        <v>25.78</v>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>52.63</v>
+        <v>52.67</v>
       </c>
       <c r="H3" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="4">
@@ -5349,22 +5349,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D4" t="n">
-        <v>24.33</v>
+        <v>24.49</v>
       </c>
       <c r="E4" t="n">
-        <v>23.43</v>
+        <v>23.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="n">
-        <v>52.55</v>
+        <v>52.57</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5">
@@ -5377,13 +5377,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="D5" t="n">
-        <v>25.03</v>
+        <v>25.68</v>
       </c>
       <c r="E5" t="n">
-        <v>23.92</v>
+        <v>24.57</v>
       </c>
       <c r="F5" t="n">
         <v>1.11</v>
@@ -5405,19 +5405,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>24.06</v>
+        <v>23.68</v>
       </c>
       <c r="E6" t="n">
-        <v>23.24</v>
+        <v>22.86</v>
       </c>
       <c r="F6" t="n">
         <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>52.21</v>
+        <v>52.22</v>
       </c>
       <c r="H6" t="n">
         <v>8.199999999999999</v>
@@ -5436,24 +5436,24 @@
         <v>22.5</v>
       </c>
       <c r="D7" t="n">
-        <v>23.01</v>
+        <v>23.44</v>
       </c>
       <c r="E7" t="n">
-        <v>21.21</v>
+        <v>21.66</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G7" t="n">
-        <v>52.22</v>
+        <v>52.16</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -5461,19 +5461,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="n">
-        <v>18.83</v>
+        <v>19.18</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67</v>
+        <v>17.02</v>
       </c>
       <c r="F8" t="n">
         <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>52.51</v>
+        <v>52.55</v>
       </c>
       <c r="H8" t="n">
         <v>21.6</v>
@@ -5481,58 +5481,58 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Hanabi</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="D9" t="n">
-        <v>11.49</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>9.970000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
-        <v>52.62</v>
+        <v>53.36</v>
       </c>
       <c r="H9" t="n">
-        <v>15.2</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hanabi</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="D10" t="n">
-        <v>6.56</v>
+        <v>11.72</v>
       </c>
       <c r="E10" t="n">
-        <v>4.02</v>
+        <v>10.19</v>
       </c>
       <c r="F10" t="n">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="G10" t="n">
-        <v>53.32</v>
+        <v>52.64</v>
       </c>
       <c r="H10" t="n">
-        <v>25.4</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="11">
@@ -5545,22 +5545,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="D11" t="n">
-        <v>21.19</v>
+        <v>21.07</v>
       </c>
       <c r="E11" t="n">
-        <v>19.07</v>
+        <v>18.96</v>
       </c>
       <c r="F11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="G11" t="n">
-        <v>50.41</v>
+        <v>50.39</v>
       </c>
       <c r="H11" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="12">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>3.23</v>
@@ -5585,7 +5585,7 @@
         <v>1.51</v>
       </c>
       <c r="G12" t="n">
-        <v>51.92</v>
+        <v>51.87</v>
       </c>
       <c r="H12" t="n">
         <v>15.1</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
         <v>2.39</v>
@@ -5613,7 +5613,7 @@
         <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>50.6</v>
+        <v>50.58</v>
       </c>
       <c r="H13" t="n">
         <v>16.4</v>
@@ -5696,19 +5696,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33.8</v>
+        <v>33.4</v>
       </c>
       <c r="D2" t="n">
-        <v>18.98</v>
+        <v>18.71</v>
       </c>
       <c r="E2" t="n">
-        <v>18.65</v>
+        <v>18.38</v>
       </c>
       <c r="F2" t="n">
         <v>0.33</v>
       </c>
       <c r="G2" t="n">
-        <v>55.58</v>
+        <v>55.52</v>
       </c>
       <c r="H2" t="n">
         <v>3.3</v>
@@ -5724,22 +5724,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D3" t="n">
-        <v>12.98</v>
+        <v>13.22</v>
       </c>
       <c r="E3" t="n">
-        <v>12.39</v>
+        <v>12.62</v>
       </c>
       <c r="F3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>54.14</v>
+        <v>54.15</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -5752,22 +5752,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="D4" t="n">
-        <v>12.94</v>
+        <v>12.9</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6</v>
+        <v>11.57</v>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>52.84</v>
+        <v>52.82</v>
       </c>
       <c r="H4" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="5">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="D5" t="n">
-        <v>11.77</v>
+        <v>11.72</v>
       </c>
       <c r="E5" t="n">
-        <v>10.49</v>
+        <v>10.44</v>
       </c>
       <c r="F5" t="n">
         <v>1.28</v>
@@ -5800,7 +5800,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -5808,22 +5808,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
-        <v>13.26</v>
+        <v>12.82</v>
       </c>
       <c r="E6" t="n">
-        <v>12.25</v>
+        <v>11.83</v>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="G6" t="n">
-        <v>52.48</v>
+        <v>52.47</v>
       </c>
       <c r="H6" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="7">
@@ -5839,16 +5839,16 @@
         <v>13.1</v>
       </c>
       <c r="D7" t="n">
-        <v>15.65</v>
+        <v>15.63</v>
       </c>
       <c r="E7" t="n">
-        <v>15.1</v>
+        <v>15.08</v>
       </c>
       <c r="F7" t="n">
         <v>0.55</v>
       </c>
       <c r="G7" t="n">
-        <v>50.97</v>
+        <v>50.96</v>
       </c>
       <c r="H7" t="n">
         <v>5.5</v>
@@ -5864,22 +5864,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="E8" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="F8" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="G8" t="n">
-        <v>52.46</v>
+        <v>52.41</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -5895,19 +5895,19 @@
         <v>10.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="E9" t="n">
         <v>0.55</v>
       </c>
       <c r="F9" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="G9" t="n">
         <v>52.36</v>
       </c>
       <c r="H9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="10">
@@ -5920,19 +5920,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="E10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="n">
         <v>0.76</v>
       </c>
       <c r="G10" t="n">
-        <v>52.09</v>
+        <v>52.05</v>
       </c>
       <c r="H10" t="n">
         <v>7.6</v>
@@ -5948,19 +5948,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="E11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="F11" t="n">
         <v>0.78</v>
       </c>
       <c r="G11" t="n">
-        <v>51.91</v>
+        <v>51.92</v>
       </c>
       <c r="H11" t="n">
         <v>7.8</v>
@@ -5979,19 +5979,19 @@
         <v>8.9</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G12" t="n">
         <v>52.14</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="13">
@@ -6007,16 +6007,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>9.75</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>9.130000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="F13" t="n">
         <v>0.62</v>
       </c>
       <c r="G13" t="n">
-        <v>50.78</v>
+        <v>50.77</v>
       </c>
       <c r="H13" t="n">
         <v>6.2</v>
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D14" t="n">
         <v>0.54</v>
@@ -6044,7 +6044,7 @@
         <v>0.44</v>
       </c>
       <c r="G14" t="n">
-        <v>52.02</v>
+        <v>52.05</v>
       </c>
       <c r="H14" t="n">
         <v>4.4</v>
@@ -6056,26 +6056,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Odette</t>
+          <t>Uranus</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="E15" t="n">
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="F15" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="G15" t="n">
-        <v>51.79</v>
+        <v>51.73</v>
       </c>
       <c r="H15" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="16">
@@ -6084,26 +6084,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Uranus</t>
+          <t>Odette</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>7.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="G16" t="n">
-        <v>51.73</v>
+        <v>51.76</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -6112,26 +6112,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Khaleed</t>
+          <t>Argus</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="E17" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="F17" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="G17" t="n">
-        <v>51.7</v>
+        <v>51.79</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -6140,26 +6140,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Argus</t>
+          <t>Khaleed</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="F18" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="G18" t="n">
         <v>51.73</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="19">
@@ -6168,26 +6168,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bane</t>
+          <t>Yu Zhong</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>5.9</v>
       </c>
       <c r="D19" t="n">
-        <v>0.43</v>
+        <v>7.87</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09</v>
+        <v>6.51</v>
       </c>
       <c r="F19" t="n">
-        <v>0.34</v>
+        <v>1.36</v>
       </c>
       <c r="G19" t="n">
-        <v>51.44</v>
+        <v>50.4</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="20">
@@ -6196,26 +6196,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Faramis</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="D20" t="n">
-        <v>0.85</v>
+        <v>2.14</v>
       </c>
       <c r="E20" t="n">
-        <v>0.66</v>
+        <v>1.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="G20" t="n">
-        <v>51.36</v>
+        <v>51.11</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -6224,26 +6224,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Yu Zhong</t>
+          <t>Bane</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="D21" t="n">
-        <v>7.95</v>
+        <v>0.43</v>
       </c>
       <c r="E21" t="n">
-        <v>6.58</v>
+        <v>0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1.37</v>
+        <v>0.34</v>
       </c>
       <c r="G21" t="n">
-        <v>50.4</v>
+        <v>51.36</v>
       </c>
       <c r="H21" t="n">
-        <v>13.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22">
@@ -6252,26 +6252,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Yve</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.13</v>
+        <v>0.31</v>
       </c>
       <c r="E22" t="n">
-        <v>1.85</v>
+        <v>0.11</v>
       </c>
       <c r="F22" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="G22" t="n">
-        <v>51.15</v>
+        <v>51.34</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -6280,26 +6280,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Popol and Kupa</t>
+          <t>Faramis</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3</v>
+        <v>0.85</v>
       </c>
       <c r="E23" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="F23" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="G23" t="n">
-        <v>51.36</v>
+        <v>51.26</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="24">
@@ -6308,26 +6308,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yve</t>
+          <t>Popol and Kupa</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5.5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E24" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G24" t="n">
         <v>51.34</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -6343,10 +6343,10 @@
         <v>5.3</v>
       </c>
       <c r="D25" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="F25" t="n">
         <v>0.6899999999999999</v>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D26" t="n">
         <v>1.53</v>
@@ -6380,7 +6380,7 @@
         <v>0.75</v>
       </c>
       <c r="G26" t="n">
-        <v>51.12</v>
+        <v>51.14</v>
       </c>
       <c r="H26" t="n">
         <v>7.5</v>
@@ -6392,26 +6392,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Clint</t>
+          <t>Thamuz</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>3.19</v>
       </c>
       <c r="E27" t="n">
-        <v>0.75</v>
+        <v>2.29</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>51.06</v>
+        <v>50.82</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -6420,26 +6420,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thamuz</t>
+          <t>Aulus</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>4.9</v>
       </c>
       <c r="D28" t="n">
-        <v>3.13</v>
+        <v>0.17</v>
       </c>
       <c r="E28" t="n">
-        <v>2.24</v>
+        <v>0.05</v>
       </c>
       <c r="F28" t="n">
-        <v>0.89</v>
+        <v>0.12</v>
       </c>
       <c r="G28" t="n">
-        <v>50.82</v>
+        <v>51.2</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29">
@@ -6448,26 +6448,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suyou</t>
+          <t>Clint</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>4.7</v>
       </c>
       <c r="D29" t="n">
-        <v>3.28</v>
+        <v>1.73</v>
       </c>
       <c r="E29" t="n">
-        <v>2.04</v>
+        <v>0.74</v>
       </c>
       <c r="F29" t="n">
-        <v>1.24</v>
+        <v>0.99</v>
       </c>
       <c r="G29" t="n">
-        <v>50.77</v>
+        <v>50.99</v>
       </c>
       <c r="H29" t="n">
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="30">
@@ -6476,26 +6476,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aulus</t>
+          <t>Suyou</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="D30" t="n">
-        <v>0.16</v>
+        <v>3.29</v>
       </c>
       <c r="E30" t="n">
-        <v>0.05</v>
+        <v>2.05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.11</v>
+        <v>1.24</v>
       </c>
       <c r="G30" t="n">
-        <v>51.1</v>
+        <v>50.77</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="31">
@@ -6520,7 +6520,7 @@
         <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>50.92</v>
+        <v>50.94</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
@@ -6536,19 +6536,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="D32" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="F32" t="n">
         <v>1.19</v>
       </c>
       <c r="G32" t="n">
-        <v>50.6</v>
+        <v>50.58</v>
       </c>
       <c r="H32" t="n">
         <v>11.9</v>
@@ -6560,26 +6560,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brody</t>
+          <t>Cyclops</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="E33" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="F33" t="n">
-        <v>0.63</v>
+        <v>1.06</v>
       </c>
       <c r="G33" t="n">
-        <v>50.91</v>
+        <v>50.83</v>
       </c>
       <c r="H33" t="n">
-        <v>6.3</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="34">
@@ -6588,26 +6588,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cyclops</t>
+          <t>Alucard</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>3.8</v>
       </c>
       <c r="D34" t="n">
-        <v>1.59</v>
+        <v>1.13</v>
       </c>
       <c r="E34" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="F34" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="G34" t="n">
-        <v>50.79</v>
+        <v>50.82</v>
       </c>
       <c r="H34" t="n">
-        <v>10.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="35">
@@ -6616,26 +6616,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Alucard</t>
+          <t>Brody</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>3.7</v>
       </c>
       <c r="D35" t="n">
-        <v>1.13</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="F35" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="G35" t="n">
-        <v>50.79</v>
+        <v>50.83</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="36">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D36" t="n">
         <v>0.44</v>
@@ -6660,7 +6660,7 @@
         <v>0.18</v>
       </c>
       <c r="G36" t="n">
-        <v>50.71</v>
+        <v>50.76</v>
       </c>
       <c r="H36" t="n">
         <v>1.8</v>
@@ -6672,26 +6672,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Edith</t>
+          <t>Terizla</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2.9</v>
       </c>
       <c r="D37" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="G37" t="n">
-        <v>50.69</v>
+        <v>50.67</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="38">
@@ -6700,26 +6700,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Terizla</t>
+          <t>Edith</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2.8</v>
       </c>
       <c r="D38" t="n">
-        <v>0.51</v>
+        <v>0.31</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="F38" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="G38" t="n">
-        <v>50.65</v>
+        <v>50.66</v>
       </c>
       <c r="H38" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="39">
@@ -6735,19 +6735,19 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="E39" t="n">
         <v>1.12</v>
       </c>
       <c r="F39" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="G39" t="n">
         <v>50.29</v>
       </c>
       <c r="H39" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="40">
@@ -6760,22 +6760,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D40" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="E40" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G40" t="n">
-        <v>50.14</v>
+        <v>50.18</v>
       </c>
       <c r="H40" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="41">
@@ -6788,13 +6788,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D41" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="E41" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="F41" t="n">
         <v>0.85</v>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D42" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="E42" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="F42" t="n">
         <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>50.02</v>
+        <v>50.01</v>
       </c>
       <c r="H42" t="n">
         <v>5</v>
@@ -6844,22 +6844,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D43" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="E43" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>50.01</v>
       </c>
       <c r="H43" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6938,22 +6938,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56</v>
+        <v>17.32</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45</v>
+        <v>16.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="n">
         <v>49.44</v>
       </c>
       <c r="H2" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -6969,16 +6969,16 @@
         <v>6.9</v>
       </c>
       <c r="D3" t="n">
-        <v>14.95</v>
+        <v>14.81</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2</v>
+        <v>13.06</v>
       </c>
       <c r="F3" t="n">
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>49.65</v>
+        <v>49.67</v>
       </c>
       <c r="H3" t="n">
         <v>17.5</v>
@@ -6990,26 +6990,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>X.Borg</t>
+          <t>Belerick</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>5.83</v>
+        <v>4.48</v>
       </c>
       <c r="E4" t="n">
-        <v>4.97</v>
+        <v>3.46</v>
       </c>
       <c r="F4" t="n">
-        <v>0.86</v>
+        <v>1.02</v>
       </c>
       <c r="G4" t="n">
-        <v>49.26</v>
+        <v>49.47</v>
       </c>
       <c r="H4" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="5">
@@ -7018,26 +7018,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Belerick</t>
+          <t>X.Borg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D5" t="n">
-        <v>4.39</v>
+        <v>5.8</v>
       </c>
       <c r="E5" t="n">
-        <v>3.38</v>
+        <v>4.94</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>49.43</v>
+        <v>49.27</v>
       </c>
       <c r="H5" t="n">
-        <v>10.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6">
@@ -7046,26 +7046,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Vale</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="F6" t="n">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="G6" t="n">
-        <v>49.87</v>
+        <v>49.9</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -7074,26 +7074,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.71</v>
+        <v>1.05</v>
       </c>
       <c r="E7" t="n">
-        <v>1.23</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="G7" t="n">
-        <v>49.7</v>
+        <v>49.84</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -7102,26 +7102,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vale</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>1.71</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05</v>
+        <v>1.23</v>
       </c>
       <c r="F8" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="G8" t="n">
-        <v>49.87</v>
+        <v>49.63</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -7134,22 +7134,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="D9" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="E9" t="n">
-        <v>7.37</v>
+        <v>7.28</v>
       </c>
       <c r="F9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G9" t="n">
-        <v>48.74</v>
+        <v>48.73</v>
       </c>
       <c r="H9" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="10">
@@ -7174,7 +7174,7 @@
         <v>0.68</v>
       </c>
       <c r="G10" t="n">
-        <v>49.8</v>
+        <v>49.79</v>
       </c>
       <c r="H10" t="n">
         <v>6.8</v>
@@ -7186,26 +7186,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.59</v>
+        <v>1.63</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>1.09</v>
       </c>
       <c r="F11" t="n">
-        <v>0.39</v>
+        <v>0.54</v>
       </c>
       <c r="G11" t="n">
-        <v>49.74</v>
+        <v>49.64</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12">
@@ -7214,26 +7214,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="n">
-        <v>1.11</v>
+        <v>0.21</v>
       </c>
       <c r="F12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="G12" t="n">
-        <v>49.61</v>
+        <v>49.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="13">
@@ -7242,26 +7242,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aldous</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2</v>
+        <v>-1.9</v>
       </c>
       <c r="D13" t="n">
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.21</v>
+        <v>0.72</v>
       </c>
       <c r="F13" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="G13" t="n">
-        <v>49.46</v>
+        <v>49.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7270,26 +7270,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Pharsa</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-2</v>
+        <v>-2.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="E14" t="n">
-        <v>0.71</v>
+        <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="G14" t="n">
-        <v>49.37</v>
+        <v>49.36</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -7298,26 +7298,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Lylia</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>-2.2</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="E15" t="n">
-        <v>1.41</v>
+        <v>0.45</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>49.2</v>
+        <v>49.33</v>
       </c>
       <c r="H15" t="n">
-        <v>6.9</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="16">
@@ -7326,26 +7326,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pharsa</t>
+          <t>Aldous</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.28</v>
+        <v>0.54</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.98</v>
+        <v>0.32</v>
       </c>
       <c r="G16" t="n">
-        <v>49.37</v>
+        <v>49.38</v>
       </c>
       <c r="H16" t="n">
-        <v>9.800000000000001</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -7354,26 +7354,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lylia</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.31</v>
+        <v>2.13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.41</v>
+        <v>1.43</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>49.29</v>
+        <v>49.14</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -7386,22 +7386,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="E18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="F18" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G18" t="n">
-        <v>49.04</v>
+        <v>49.02</v>
       </c>
       <c r="H18" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="19">
@@ -7414,22 +7414,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="E19" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="F19" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="G19" t="n">
-        <v>48.71</v>
+        <v>48.75</v>
       </c>
       <c r="H19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="20">
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="E20" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="F20" t="n">
         <v>0.52</v>
       </c>
       <c r="G20" t="n">
-        <v>48.73</v>
+        <v>48.72</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
@@ -7466,26 +7466,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Chang'e</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-4.4</v>
+        <v>-4.6</v>
       </c>
       <c r="D21" t="n">
-        <v>2.75</v>
+        <v>0.96</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3</v>
+        <v>0.24</v>
       </c>
       <c r="F21" t="n">
-        <v>1.45</v>
+        <v>0.72</v>
       </c>
       <c r="G21" t="n">
-        <v>48.67</v>
+        <v>48.79</v>
       </c>
       <c r="H21" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="22">
@@ -7494,26 +7494,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chang'e</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>-4.7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.96</v>
+        <v>2.67</v>
       </c>
       <c r="E22" t="n">
-        <v>0.24</v>
+        <v>1.25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.72</v>
+        <v>1.42</v>
       </c>
       <c r="G22" t="n">
-        <v>48.77</v>
+        <v>48.61</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="23">
@@ -7554,22 +7554,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
       <c r="D24" t="n">
-        <v>6.96</v>
+        <v>6.97</v>
       </c>
       <c r="E24" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="F24" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="G24" t="n">
-        <v>47.94</v>
+        <v>47.88</v>
       </c>
       <c r="H24" t="n">
-        <v>17.1</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="25">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-6.1</v>
+        <v>-6</v>
       </c>
       <c r="D25" t="n">
         <v>0.82</v>
@@ -7594,7 +7594,7 @@
         <v>0.53</v>
       </c>
       <c r="G25" t="n">
-        <v>48.42</v>
+        <v>48.45</v>
       </c>
       <c r="H25" t="n">
         <v>5.3</v>
@@ -7606,26 +7606,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Beatrix</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>-6.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.22</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="F26" t="n">
-        <v>0.18</v>
+        <v>0.65</v>
       </c>
       <c r="G26" t="n">
-        <v>48.43</v>
+        <v>48.41</v>
       </c>
       <c r="H26" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="27">
@@ -7634,26 +7634,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Beatrix</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-6.2</v>
+        <v>-6.5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8</v>
+        <v>0.21</v>
       </c>
       <c r="E27" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="F27" t="n">
-        <v>0.65</v>
+        <v>0.17</v>
       </c>
       <c r="G27" t="n">
-        <v>48.41</v>
+        <v>48.36</v>
       </c>
       <c r="H27" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="28">
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-6.9</v>
+        <v>-7.3</v>
       </c>
       <c r="D28" t="n">
         <v>0.55</v>
@@ -7678,7 +7678,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>48.19</v>
+        <v>48.1</v>
       </c>
       <c r="H28" t="n">
         <v>0.7</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="E29" t="n">
         <v>0.15</v>
       </c>
       <c r="F29" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G29" t="n">
-        <v>48.15</v>
+        <v>48.13</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -7718,26 +7718,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Harley</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-7.7</v>
+        <v>-7.5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.41</v>
+        <v>1.34</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="F30" t="n">
-        <v>0.34</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>48.07</v>
+        <v>48.02</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -7746,26 +7746,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Harley</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-7.7</v>
+        <v>-7.6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.32</v>
+        <v>0.41</v>
       </c>
       <c r="E31" t="n">
-        <v>0.62</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7</v>
+        <v>0.34</v>
       </c>
       <c r="G31" t="n">
-        <v>47.97</v>
+        <v>48.09</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="32">
@@ -7774,26 +7774,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Cici</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>-8.4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.34</v>
+        <v>1.49</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06</v>
+        <v>0.89</v>
       </c>
       <c r="F32" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
       <c r="G32" t="n">
-        <v>47.9</v>
+        <v>47.76</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -7802,26 +7802,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cici</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>-8.5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>0.33</v>
       </c>
       <c r="E33" t="n">
-        <v>0.89</v>
+        <v>0.06</v>
       </c>
       <c r="F33" t="n">
-        <v>0.61</v>
+        <v>0.27</v>
       </c>
       <c r="G33" t="n">
-        <v>47.74</v>
+        <v>47.87</v>
       </c>
       <c r="H33" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="34">
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="D34" t="n">
         <v>1.4</v>
@@ -7846,7 +7846,7 @@
         <v>0.9</v>
       </c>
       <c r="G34" t="n">
-        <v>47.77</v>
+        <v>47.73</v>
       </c>
       <c r="H34" t="n">
         <v>9</v>
@@ -7862,19 +7862,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-8.6</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F35" t="n">
         <v>0.16</v>
       </c>
       <c r="G35" t="n">
-        <v>47.85</v>
+        <v>47.78</v>
       </c>
       <c r="H35" t="n">
         <v>1.6</v>
@@ -7893,24 +7893,24 @@
         <v>-8.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="E36" t="n">
         <v>0.24</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="G36" t="n">
-        <v>47.74</v>
+        <v>47.73</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.5</v>
       </c>
       <c r="D37" t="n">
         <v>0.63</v>
@@ -7930,7 +7930,7 @@
         <v>0.44</v>
       </c>
       <c r="G37" t="n">
-        <v>47.51</v>
+        <v>47.6</v>
       </c>
       <c r="H37" t="n">
         <v>4.4</v>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-10.6</v>
+        <v>-10.8</v>
       </c>
       <c r="D2" t="n">
         <v>0.76</v>
@@ -8024,7 +8024,7 @@
         <v>0.48</v>
       </c>
       <c r="G2" t="n">
-        <v>47.3</v>
+        <v>47.27</v>
       </c>
       <c r="H2" t="n">
         <v>4.8</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-12</v>
+        <v>-11.8</v>
       </c>
       <c r="D3" t="n">
         <v>0.93</v>
@@ -8052,7 +8052,7 @@
         <v>0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>46.98</v>
+        <v>47.04</v>
       </c>
       <c r="H3" t="n">
         <v>7.8</v>
@@ -8080,7 +8080,7 @@
         <v>0.17</v>
       </c>
       <c r="G4" t="n">
-        <v>46.98</v>
+        <v>46.96</v>
       </c>
       <c r="H4" t="n">
         <v>1.7</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-12.4</v>
+        <v>-12.5</v>
       </c>
       <c r="D5" t="n">
         <v>0.57</v>
@@ -8108,7 +8108,7 @@
         <v>0.43</v>
       </c>
       <c r="G5" t="n">
-        <v>46.88</v>
+        <v>46.85</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-12.7</v>
+        <v>-12.6</v>
       </c>
       <c r="D6" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="E6" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="F6" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G6" t="n">
-        <v>46.79</v>
+        <v>46.81</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7">
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-12.9</v>
+        <v>-12.8</v>
       </c>
       <c r="D7" t="n">
         <v>0.89</v>
@@ -8164,7 +8164,7 @@
         <v>0.64</v>
       </c>
       <c r="G7" t="n">
-        <v>46.74</v>
+        <v>46.77</v>
       </c>
       <c r="H7" t="n">
         <v>6.4</v>
@@ -8180,19 +8180,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-13.7</v>
+        <v>-13.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="F8" t="n">
         <v>0.55</v>
       </c>
       <c r="G8" t="n">
-        <v>46.53</v>
+        <v>46.5</v>
       </c>
       <c r="H8" t="n">
         <v>5.5</v>
@@ -8208,22 +8208,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-14.5</v>
+        <v>-14.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="E9" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>46.28</v>
+        <v>46.34</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="10">
@@ -8236,19 +8236,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-15.3</v>
+        <v>-15.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="F10" t="n">
         <v>0.48</v>
       </c>
       <c r="G10" t="n">
-        <v>46.1</v>
+        <v>46.11</v>
       </c>
       <c r="H10" t="n">
         <v>4.8</v>
@@ -8260,26 +8260,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wanwan</t>
+          <t>Kalea</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-15.4</v>
+        <v>-15.5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>2.06</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>1.77</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="G11" t="n">
-        <v>46.13</v>
+        <v>45.87</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -8288,26 +8288,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kalea</t>
+          <t>Wanwan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-15.6</v>
+        <v>-15.7</v>
       </c>
       <c r="D12" t="n">
-        <v>2.09</v>
+        <v>0.4</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>45.83</v>
+        <v>46.04</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-16</v>
+        <v>-16.5</v>
       </c>
       <c r="D13" t="n">
         <v>0.34</v>
@@ -8332,7 +8332,7 @@
         <v>0.24</v>
       </c>
       <c r="G13" t="n">
-        <v>46</v>
+        <v>45.88</v>
       </c>
       <c r="H13" t="n">
         <v>2.4</v>
@@ -8348,7 +8348,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-18.5</v>
+        <v>-19</v>
       </c>
       <c r="D14" t="n">
         <v>0.31</v>
@@ -8360,7 +8360,7 @@
         <v>0.25</v>
       </c>
       <c r="G14" t="n">
-        <v>45.37</v>
+        <v>45.25</v>
       </c>
       <c r="H14" t="n">
         <v>2.5</v>
@@ -8376,22 +8376,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-20.6</v>
+        <v>-20.2</v>
       </c>
       <c r="D15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="E15" t="n">
         <v>1.3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G15" t="n">
-        <v>44.71</v>
+        <v>44.8</v>
       </c>
       <c r="H15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -8404,22 +8404,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-21.1</v>
+        <v>-21.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="F16" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G16" t="n">
-        <v>44.71</v>
+        <v>44.66</v>
       </c>
       <c r="H16" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17">
@@ -8432,22 +8432,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-22</v>
+        <v>-22.2</v>
       </c>
       <c r="D17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="E17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="F17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="G17" t="n">
-        <v>44.3</v>
+        <v>44.26</v>
       </c>
       <c r="H17" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="18">
@@ -8463,19 +8463,19 @@
         <v>-22.7</v>
       </c>
       <c r="D18" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="E18" t="n">
         <v>0.34</v>
       </c>
       <c r="F18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="G18" t="n">
         <v>44.3</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19">
@@ -8516,22 +8516,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-25.4</v>
+        <v>-25.8</v>
       </c>
       <c r="D20" t="n">
-        <v>5.35</v>
+        <v>5.48</v>
       </c>
       <c r="E20" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="G20" t="n">
-        <v>43.06</v>
+        <v>42.96</v>
       </c>
       <c r="H20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="21">
@@ -8544,19 +8544,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-28.2</v>
+        <v>-28.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="E21" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="F21" t="n">
         <v>0.23</v>
       </c>
       <c r="G21" t="n">
-        <v>42.91</v>
+        <v>42.95</v>
       </c>
       <c r="H21" t="n">
         <v>2.3</v>
@@ -8575,19 +8575,19 @@
         <v>-28.9</v>
       </c>
       <c r="D22" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="E22" t="n">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G22" t="n">
-        <v>42.43</v>
+        <v>42.44</v>
       </c>
       <c r="H22" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="23">
@@ -8600,22 +8600,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-32.1</v>
+        <v>-32</v>
       </c>
       <c r="D23" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="E23" t="n">
         <v>0.16</v>
       </c>
       <c r="F23" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="G23" t="n">
-        <v>41.97</v>
+        <v>42.01</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -8695,19 +8695,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="E2" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F2" t="n">
         <v>0.2</v>
       </c>
       <c r="G2" t="n">
-        <v>56.48</v>
+        <v>56.46</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -8743,7 +8743,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -8751,19 +8751,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="E4" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="F4" t="n">
         <v>0.45</v>
       </c>
       <c r="G4" t="n">
-        <v>54.61</v>
+        <v>54.58</v>
       </c>
       <c r="H4" t="n">
         <v>4.5</v>
@@ -8779,19 +8779,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D5" t="n">
-        <v>6.64</v>
+        <v>6.53</v>
       </c>
       <c r="E5" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="F5" t="n">
         <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>53.55</v>
+        <v>53.59</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -8810,16 +8810,16 @@
         <v>12.4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F6" t="n">
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>52.97</v>
+        <v>52.96</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -8835,22 +8835,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="E7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G7" t="n">
-        <v>52.76</v>
+        <v>52.8</v>
       </c>
       <c r="H7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="8">
@@ -8863,22 +8863,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="F8" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="G8" t="n">
-        <v>52.79</v>
+        <v>52.81</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -8894,16 +8894,16 @@
         <v>11.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="F9" t="n">
         <v>0.82</v>
       </c>
       <c r="G9" t="n">
-        <v>52.74</v>
+        <v>52.73</v>
       </c>
       <c r="H9" t="n">
         <v>8.199999999999999</v>
@@ -8986,19 +8986,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="D2" t="n">
-        <v>92.97</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>92.38</v>
+        <v>92.34</v>
       </c>
       <c r="F2" t="n">
         <v>0.59</v>
       </c>
       <c r="G2" t="n">
-        <v>54.4</v>
+        <v>54.46</v>
       </c>
       <c r="H2" t="n">
         <v>5.9</v>
@@ -9014,22 +9014,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>83.81</v>
+        <v>84.09</v>
       </c>
       <c r="E3" t="n">
-        <v>82.65000000000001</v>
+        <v>82.95</v>
       </c>
       <c r="F3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
-        <v>53.55</v>
+        <v>53.6</v>
       </c>
       <c r="H3" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="4">
@@ -9042,22 +9042,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
-        <v>85.90000000000001</v>
+        <v>85.75</v>
       </c>
       <c r="E4" t="n">
-        <v>84.93000000000001</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="G4" t="n">
-        <v>50.67</v>
+        <v>50.7</v>
       </c>
       <c r="H4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
@@ -9073,16 +9073,16 @@
         <v>35.4</v>
       </c>
       <c r="D5" t="n">
-        <v>51.55</v>
+        <v>51.54</v>
       </c>
       <c r="E5" t="n">
-        <v>50.17</v>
+        <v>50.16</v>
       </c>
       <c r="F5" t="n">
         <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>51.2</v>
+        <v>51.21</v>
       </c>
       <c r="H5" t="n">
         <v>13.8</v>
@@ -9098,19 +9098,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>33.5</v>
+        <v>33.1</v>
       </c>
       <c r="D6" t="n">
-        <v>36.76</v>
+        <v>36.27</v>
       </c>
       <c r="E6" t="n">
-        <v>35.64</v>
+        <v>35.15</v>
       </c>
       <c r="F6" t="n">
         <v>1.12</v>
       </c>
       <c r="G6" t="n">
-        <v>52.88</v>
+        <v>52.86</v>
       </c>
       <c r="H6" t="n">
         <v>11.2</v>
@@ -9126,13 +9126,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="D7" t="n">
-        <v>48.34</v>
+        <v>48.12</v>
       </c>
       <c r="E7" t="n">
-        <v>47.56</v>
+        <v>47.34</v>
       </c>
       <c r="F7" t="n">
         <v>0.78</v>
@@ -9154,22 +9154,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="D8" t="n">
-        <v>41.59</v>
+        <v>41.6</v>
       </c>
       <c r="E8" t="n">
-        <v>40.49</v>
+        <v>40.51</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>51.17</v>
+        <v>51.15</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="9">
@@ -9182,19 +9182,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="D9" t="n">
-        <v>39.62</v>
+        <v>39.5</v>
       </c>
       <c r="E9" t="n">
-        <v>37.5</v>
+        <v>37.38</v>
       </c>
       <c r="F9" t="n">
         <v>2.12</v>
       </c>
       <c r="G9" t="n">
-        <v>51.06</v>
+        <v>51.03</v>
       </c>
       <c r="H9" t="n">
         <v>21.2</v>
@@ -9277,19 +9277,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-8.5</v>
+        <v>-8.6</v>
       </c>
       <c r="D2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="E2" t="n">
-        <v>6.34</v>
+        <v>6.37</v>
       </c>
       <c r="F2" t="n">
         <v>2.04</v>
       </c>
       <c r="G2" t="n">
-        <v>46.95</v>
+        <v>46.93</v>
       </c>
       <c r="H2" t="n">
         <v>20.4</v>
@@ -9297,7 +9297,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -9305,22 +9305,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-9.4</v>
+        <v>-9.6</v>
       </c>
       <c r="D3" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
       <c r="E3" t="n">
-        <v>10.59</v>
+        <v>10.53</v>
       </c>
       <c r="F3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>46.13</v>
+        <v>46.09</v>
       </c>
       <c r="H3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="4">
@@ -9333,22 +9333,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-30</v>
+        <v>-30.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="E4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="G4" t="n">
-        <v>42.39</v>
+        <v>42.34</v>
       </c>
       <c r="H4" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
